--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486921_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486921_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2854</v>
+        <v>6.5275</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8211</v>
+        <v>8.413500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5357</v>
+        <v>-1.886</v>
       </c>
       <c r="G2" t="n">
-        <v>1.767</v>
+        <v>6.7611</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5808</v>
+        <v>5.022</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1863</v>
+        <v>1.7392</v>
       </c>
       <c r="J2" t="n">
-        <v>3.926</v>
+        <v>7.6732</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4401</v>
+        <v>5.2397</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4859</v>
+        <v>2.4335</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1589</v>
+        <v>-0.9121</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8593</v>
+        <v>-0.2177</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2996</v>
+        <v>-0.6943</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>3.929</v>
+        <v>0.9182</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7699</v>
+        <v>1.1777</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1591</v>
+        <v>-0.2594</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1786</v>
+        <v>-1.7679</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3573</v>
+        <v>0.5893</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5302</v>
+        <v>5.307</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8905</v>
+        <v>5.0551</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3603</v>
+        <v>0.252</v>
       </c>
       <c r="G3" t="n">
-        <v>6.7611</v>
+        <v>2.4845</v>
       </c>
       <c r="H3" t="n">
-        <v>5.022</v>
+        <v>1.5055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7392</v>
+        <v>0.979</v>
       </c>
       <c r="J3" t="n">
-        <v>7.6732</v>
+        <v>3.1176</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2397</v>
+        <v>1.7232</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4335</v>
+        <v>1.3943</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9121</v>
+        <v>-0.6331</v>
       </c>
       <c r="N3" t="n">
         <v>-0.2177</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6943</v>
+        <v>-0.4154</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.079</v>
+        <v>1.1449</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6546999999999999</v>
+        <v>1.1079</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7337</v>
+        <v>0.037</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.7679</v>
+        <v>0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>0.8295</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3573</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3523</v>
+        <v>4.9439</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1597</v>
+        <v>6.0428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1927</v>
+        <v>-1.0989</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4845</v>
+        <v>1.767</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5055</v>
+        <v>0.5808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.979</v>
+        <v>1.1863</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1176</v>
+        <v>3.926</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7232</v>
+        <v>2.4401</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3943</v>
+        <v>1.4859</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6331</v>
+        <v>-2.1589</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2177</v>
+        <v>-1.8593</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4154</v>
+        <v>-0.2996</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1903</v>
+        <v>1.5875</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2125</v>
+        <v>0.9916</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0223</v>
+        <v>0.5959</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8295</v>
+        <v>2.3573</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2825</v>
+        <v>4.7595</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7086</v>
+        <v>5.1856</v>
       </c>
       <c r="F5" t="n">
         <v>-0.4261</v>
@@ -844,10 +844,10 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7899</v>
+        <v>1.2669</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9176</v>
+        <v>1.3946</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1277</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.069</v>
+        <v>4.6496</v>
       </c>
       <c r="E6" t="n">
-        <v>3.961</v>
+        <v>4.2748</v>
       </c>
       <c r="F6" t="n">
-        <v>0.108</v>
+        <v>0.3748</v>
       </c>
       <c r="G6" t="n">
         <v>3.5266</v>
@@ -922,13 +922,13 @@
         <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.012</v>
+        <v>0.5686</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3176</v>
+        <v>0.6314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3296</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.3491</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.0441</v>
+        <v>4.1068</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7359</v>
+        <v>2.1543</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3082</v>
+        <v>1.9525</v>
       </c>
       <c r="G7" t="n">
         <v>1.3056</v>
@@ -1000,13 +1000,13 @@
         <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3011</v>
+        <v>1.3638</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3098</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9912</v>
+        <v>0.6355</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0708</v>
+        <v>0.5452</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.3179</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7296</v>
+        <v>0.8631</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7911</v>
+        <v>-0.527</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7624</v>
+        <v>-1.8555</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0287</v>
+        <v>1.3284</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5631</v>
+        <v>1.0112</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2657</v>
+        <v>-0.1065</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8288</v>
+        <v>1.1177</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3542</v>
+        <v>-1.5382</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4967</v>
+        <v>-1.7489</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8575</v>
+        <v>0.2107</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.3122</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.3389</v>
+        <v>-1.2321</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1802</v>
+        <v>0.4562</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5992</v>
+        <v>0.5532</v>
       </c>
       <c r="V8" t="n">
-        <v>3.9938</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5359</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2306</v>
+        <v>-0.135</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9455</v>
+        <v>-0.4496</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7149</v>
+        <v>0.3146</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.527</v>
+        <v>-0.7911</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8555</v>
+        <v>-0.7624</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3284</v>
+        <v>-0.0287</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0112</v>
+        <v>0.5631</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1065</v>
+        <v>-0.2657</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1177</v>
+        <v>0.8288</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5382</v>
+        <v>-1.3542</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7489</v>
+        <v>-0.4967</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2107</v>
+        <v>-0.8575</v>
       </c>
       <c r="P9" t="n">
-        <v>0.616</v>
+        <v>-4.3122</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2321</v>
+        <v>-5.3389</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3196</v>
+        <v>0.9745</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7246</v>
+        <v>0.7903</v>
       </c>
       <c r="U9" t="n">
-        <v>0.405</v>
+        <v>0.1842</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.9938</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.5359</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.146</v>
+        <v>-1.2952</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.361</v>
+        <v>-1.6288</v>
       </c>
       <c r="F10" t="n">
-        <v>0.215</v>
+        <v>0.3336</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5389</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0527</v>
+        <v>0.7981</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3216</v>
+        <v>0.4106</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2689</v>
+        <v>0.3875</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.24</v>
+        <v>-2.3916</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6567</v>
+        <v>-2.0751</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5833</v>
+        <v>-0.3165</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1155</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.972</v>
+        <v>0.8204</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9336</v>
+        <v>0.5152</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0384</v>
+        <v>0.3052</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4805</v>
@@ -1348,16 +1348,16 @@
         <v>27.0177</v>
       </c>
       <c r="E12" t="n">
-        <v>26.6548</v>
+        <v>26.65470000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.363</v>
+        <v>0.3631000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>12.3382</v>
       </c>
       <c r="H12" t="n">
-        <v>4.445000000000001</v>
+        <v>4.444999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>7.893299999999999</v>
@@ -1375,7 +1375,7 @@
         <v>-10.8448</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.0054</v>
+        <v>-9.005400000000002</v>
       </c>
       <c r="O12" t="n">
         <v>-1.8393</v>
@@ -1390,13 +1390,13 @@
         <v>13.3472</v>
       </c>
       <c r="S12" t="n">
-        <v>9.899199999999999</v>
+        <v>9.899099999999999</v>
       </c>
       <c r="T12" t="n">
         <v>7.6506</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2485</v>
+        <v>2.2486</v>
       </c>
       <c r="V12" t="n">
         <v>3.7535</v>
@@ -1405,7 +1405,7 @@
         <v>8.141499999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.388</v>
+        <v>-4.388000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.686</v>
+        <v>2.4436</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3157</v>
+        <v>4.0019</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6297</v>
+        <v>-1.5583</v>
       </c>
       <c r="G13" t="n">
         <v>1.1467</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1383</v>
+        <v>-0.3807</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5461</v>
+        <v>0.2323</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6844</v>
+        <v>-0.613</v>
       </c>
       <c r="V13" t="n">
         <v>0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4207</v>
+        <v>0.8642</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4591</v>
+        <v>4.2959</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8798</v>
+        <v>-3.4317</v>
       </c>
       <c r="G14" t="n">
         <v>1.1666</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1417</v>
+        <v>-1.8568</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3097</v>
+        <v>-0.4729</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.832</v>
+        <v>-1.3839</v>
       </c>
       <c r="V14" t="n">
         <v>0.9384</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4732</v>
+        <v>-1.5045</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4873</v>
+        <v>-0.6965</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9858</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0648</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6137</v>
+        <v>-0.6451</v>
       </c>
       <c r="T15" t="n">
-        <v>0.244</v>
+        <v>0.0348</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8577</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0381</v>
+        <v>-1.9329</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1253</v>
+        <v>0.6835</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1634</v>
+        <v>-2.6164</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.584</v>
+        <v>0.9742</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3181</v>
+        <v>1.729</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9021</v>
+        <v>-0.7548</v>
       </c>
       <c r="J16" t="n">
-        <v>0.401</v>
+        <v>2.5545</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7038</v>
+        <v>2.4756</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3027</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.985</v>
+        <v>-1.5803</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3857</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5993</v>
+        <v>-0.8338</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3796</v>
+        <v>-1.326</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4328</v>
+        <v>-0.6471</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0532</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.3491</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3716</v>
+        <v>0.8295</v>
       </c>
       <c r="X16" t="n">
         <v>-1.1786</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4298</v>
+        <v>-2.5365</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4743</v>
+        <v>0.0002</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9041</v>
+        <v>-2.5367</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9742</v>
+        <v>-0.5238</v>
       </c>
       <c r="H17" t="n">
-        <v>1.729</v>
+        <v>-0.2107</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7548</v>
+        <v>-0.313</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5545</v>
+        <v>2.177</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4756</v>
+        <v>1.7038</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0789</v>
+        <v>0.4732</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5803</v>
+        <v>-2.7007</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-1.9145</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8338</v>
+        <v>-0.7863</v>
       </c>
       <c r="P17" t="n">
         <v>-1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8229</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8563</v>
+        <v>-0.2753</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9665</v>
+        <v>-0.5054</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8295</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
         <v>-1.1786</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.5829</v>
+        <v>-3.6736</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7527</v>
+        <v>0.5435</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3356</v>
+        <v>-4.2171</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6188</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5719</v>
+        <v>-0.6626</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0464</v>
+        <v>-0.1628</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6183</v>
+        <v>-0.4997</v>
       </c>
       <c r="V18" t="n">
         <v>-2.0082</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7325</v>
+        <v>-4.1407</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8366</v>
+        <v>-1.8621</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8959</v>
+        <v>-2.2786</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5238</v>
+        <v>-2.584</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2107</v>
+        <v>0.3181</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.313</v>
+        <v>-2.9021</v>
       </c>
       <c r="J19" t="n">
-        <v>2.177</v>
+        <v>0.401</v>
       </c>
       <c r="K19" t="n">
         <v>1.7038</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4732</v>
+        <v>-1.3027</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7007</v>
+        <v>-2.985</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9145</v>
+        <v>-1.3857</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7863</v>
+        <v>-1.5993</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9767</v>
+        <v>0.277</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1121</v>
+        <v>0.4454</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8646</v>
+        <v>-0.1683</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>0.3716</v>
       </c>
       <c r="X19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.864</v>
+        <v>-4.9086</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7989</v>
+        <v>-2.3805</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0651</v>
+        <v>-2.5281</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7045</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.3115</v>
+        <v>-1.3561</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1857</v>
+        <v>-0.7673</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1258</v>
+        <v>-0.5888</v>
       </c>
       <c r="V20" t="n">
         <v>1.1786</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.1624</v>
+        <v>-9.5365</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.3672</v>
+        <v>-4.9488</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.7951</v>
+        <v>-4.5876</v>
       </c>
       <c r="G21" t="n">
         <v>-6.1298</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.702</v>
+        <v>-1.0761</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.054</v>
+        <v>-0.6355</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6481</v>
+        <v>-0.4406</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9466</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-27.0176</v>
+        <v>-24.9255</v>
       </c>
       <c r="E22" t="n">
         <v>-0.3629000000000016</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.6545</v>
+        <v>-24.5625</v>
       </c>
       <c r="G22" t="n">
         <v>-12.3382</v>
@@ -2158,7 +2158,7 @@
         <v>-13.4506</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.732600000000001</v>
+        <v>-9.7326</v>
       </c>
       <c r="P22" t="n">
         <v>-1.0269</v>
@@ -2170,13 +2170,13 @@
         <v>12.3204</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.899100000000001</v>
+        <v>-7.8071</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.2485</v>
+        <v>-2.2484</v>
       </c>
       <c r="U22" t="n">
-        <v>-7.6506</v>
+        <v>-5.5585</v>
       </c>
       <c r="V22" t="n">
         <v>-3.7537</v>
